--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:25</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:20</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-09-29 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>28</v>
+        <v>280.05</v>
       </c>
     </row>
     <row r="3">
@@ -588,7 +588,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27.61</v>
+        <v>276.11</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27.1</v>
+        <v>271.05</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24.04</v>
+        <v>240.37</v>
       </c>
     </row>
     <row r="6">
@@ -639,7 +639,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22.63</v>
+        <v>226.28</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>22.55</v>
+        <v>225.52</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.98</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="9">
@@ -690,7 +690,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20.54</v>
+        <v>205.44</v>
       </c>
     </row>
     <row r="10">
@@ -707,7 +707,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>20.04</v>
+        <v>200.36</v>
       </c>
     </row>
     <row r="11">
@@ -724,7 +724,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>19.58</v>
+        <v>195.77</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>19</v>
+        <v>189.96</v>
       </c>
     </row>
     <row r="13">
@@ -758,7 +758,7 @@
         <v>2024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.94</v>
+        <v>189.44</v>
       </c>
     </row>
     <row r="14">
@@ -775,7 +775,7 @@
         <v>2024</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.53</v>
+        <v>175.3</v>
       </c>
     </row>
     <row r="15">
@@ -792,7 +792,7 @@
         <v>2024</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.78</v>
+        <v>167.85</v>
       </c>
     </row>
     <row r="16">
@@ -809,7 +809,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15.43</v>
+        <v>154.27</v>
       </c>
     </row>
     <row r="17">
@@ -826,7 +826,7 @@
         <v>2024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15.34</v>
+        <v>153.42</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
         <v>2024</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.31</v>
+        <v>153.08</v>
       </c>
     </row>
     <row r="19">
@@ -860,7 +860,7 @@
         <v>2024</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.11</v>
+        <v>151.14</v>
       </c>
     </row>
     <row r="20">
@@ -877,7 +877,7 @@
         <v>2024</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14.54</v>
+        <v>145.36</v>
       </c>
     </row>
     <row r="21">
@@ -894,7 +894,7 @@
         <v>2024</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.51</v>
+        <v>145.06</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>2024</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13.8</v>
+        <v>138.01</v>
       </c>
     </row>
     <row r="23">
@@ -928,7 +928,7 @@
         <v>2024</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13.55</v>
+        <v>135.52</v>
       </c>
     </row>
     <row r="24">
@@ -945,7 +945,7 @@
         <v>2024</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13.22</v>
+        <v>132.24</v>
       </c>
     </row>
     <row r="25">
@@ -962,7 +962,7 @@
         <v>2024</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13.16</v>
+        <v>131.57</v>
       </c>
     </row>
     <row r="26">
@@ -979,7 +979,7 @@
         <v>2024</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>13.11</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="27">
@@ -996,7 +996,7 @@
         <v>2024</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>12.68</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="28">
@@ -1013,7 +1013,7 @@
         <v>2024</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>12.45</v>
+        <v>124.54</v>
       </c>
     </row>
     <row r="29">
@@ -1030,7 +1030,7 @@
         <v>2024</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12.39</v>
+        <v>123.89</v>
       </c>
     </row>
     <row r="30">
@@ -1047,7 +1047,7 @@
         <v>2024</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11.28</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="31">
@@ -1064,7 +1064,7 @@
         <v>2024</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11.19</v>
+        <v>111.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:03</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:04</t>
+    <t xml:space="preserve">2026-10-05 07:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
